--- a/files/九龙-长沙湾-映筑.xlsx
+++ b/files/九龙-长沙湾-映筑.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="映筑 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1005,7 +869,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1051,7 +915,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1097,7 +961,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1143,7 +1007,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1235,7 +1099,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1327,7 +1191,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1373,7 +1237,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1419,7 +1283,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1557,7 +1421,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1603,7 +1467,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-26</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1649,7 +1513,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1695,7 +1559,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1741,7 +1605,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1879,7 +1743,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1925,7 +1789,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1971,7 +1835,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2109,7 +1973,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2155,7 +2019,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2201,7 +2065,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2247,7 +2111,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2293,7 +2157,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2431,7 +2295,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2477,7 +2341,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2523,7 +2387,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2661,7 +2525,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2707,7 +2571,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2753,7 +2617,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2799,7 +2663,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2845,7 +2709,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2983,7 +2847,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3029,7 +2893,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3075,7 +2939,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3213,7 +3077,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3259,7 +3123,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3305,7 +3169,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3351,7 +3215,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3397,7 +3261,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3535,7 +3399,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3581,7 +3445,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3627,7 +3491,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3765,7 +3629,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3811,7 +3675,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3857,7 +3721,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3903,7 +3767,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3949,7 +3813,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4087,7 +3951,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4133,7 +3997,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4179,7 +4043,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4317,7 +4181,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4363,7 +4227,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4409,7 +4273,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4455,7 +4319,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4501,7 +4365,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4547,7 +4411,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4639,7 +4503,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4731,7 +4595,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4823,7 +4687,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4869,7 +4733,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4915,7 +4779,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4961,7 +4825,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5007,7 +4871,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5053,7 +4917,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5099,7 +4963,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5191,7 +5055,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5237,7 +5101,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5283,7 +5147,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5375,7 +5239,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5421,7 +5285,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5467,7 +5331,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5513,7 +5377,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5559,7 +5423,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5605,7 +5469,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5743,7 +5607,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5789,7 +5653,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5835,7 +5699,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5927,7 +5791,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6019,7 +5883,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6065,7 +5929,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6111,7 +5975,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6157,7 +6021,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6203,7 +6067,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6249,7 +6113,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6295,7 +6159,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6341,7 +6205,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6387,7 +6251,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6479,7 +6343,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6525,7 +6389,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6571,7 +6435,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6617,7 +6481,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6663,7 +6527,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6709,7 +6573,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6755,7 +6619,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6847,7 +6711,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6893,7 +6757,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6939,7 +6803,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7031,7 +6895,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7077,7 +6941,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7123,7 +6987,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7169,7 +7033,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7215,7 +7079,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7307,7 +7171,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7399,7 +7263,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7445,7 +7309,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7491,7 +7355,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7583,7 +7447,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7629,7 +7493,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7675,7 +7539,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7721,7 +7585,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7767,7 +7631,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7813,7 +7677,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7859,7 +7723,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7951,7 +7815,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -7997,7 +7861,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8043,7 +7907,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8135,7 +7999,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8181,7 +8045,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8227,7 +8091,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8273,7 +8137,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8319,7 +8183,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8365,7 +8229,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8411,7 +8275,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8503,7 +8367,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8549,7 +8413,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8595,7 +8459,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8733,7 +8597,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8779,7 +8643,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -8825,7 +8689,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -8871,7 +8735,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -8963,7 +8827,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -9009,7 +8873,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9055,7 +8919,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9101,7 +8965,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9147,7 +9011,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9239,7 +9103,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -9331,7 +9195,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9423,7 +9287,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9469,7 +9333,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9515,7 +9379,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9561,7 +9425,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9607,7 +9471,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9653,7 +9517,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -9699,7 +9563,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -9791,7 +9655,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -9837,7 +9701,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -9883,7 +9747,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -9929,7 +9793,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -10021,7 +9885,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10067,7 +9931,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10113,7 +9977,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10159,7 +10023,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10251,7 +10115,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-22</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10343,7 +10207,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10389,7 +10253,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -10435,7 +10299,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10527,7 +10391,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -10665,7 +10529,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10711,7 +10575,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -10757,7 +10621,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -10803,7 +10667,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -10895,7 +10759,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -10941,7 +10805,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -10987,7 +10851,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11033,7 +10897,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11079,7 +10943,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11125,7 +10989,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -11217,7 +11081,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-22</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -11263,7 +11127,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -11309,7 +11173,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -11355,7 +11219,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11447,7 +11311,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11493,7 +11357,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -11539,7 +11403,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -11585,7 +11449,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -11631,7 +11495,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -11677,7 +11541,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -11769,7 +11633,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -11815,7 +11679,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-22</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -11861,7 +11725,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -11907,7 +11771,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -11999,7 +11863,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -12045,7 +11909,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -12091,7 +11955,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -12137,7 +12001,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12183,7 +12047,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -12229,7 +12093,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -12321,7 +12185,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -12367,7 +12231,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12413,7 +12277,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12459,7 +12323,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -12597,7 +12461,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -12643,7 +12507,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -12735,7 +12599,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -12781,7 +12645,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -12873,7 +12737,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -12965,7 +12829,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -13011,7 +12875,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -13057,7 +12921,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -13103,7 +12967,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -13149,7 +13013,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -13195,7 +13059,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -13241,7 +13105,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -13287,7 +13151,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -13379,7 +13243,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -13425,7 +13289,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -13517,7 +13381,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -13563,7 +13427,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -13609,7 +13473,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -13655,7 +13519,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -13701,7 +13565,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -13747,7 +13611,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -13839,7 +13703,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -13885,7 +13749,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -13931,7 +13795,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -14023,7 +13887,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -14069,7 +13933,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -14115,7 +13979,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -14161,7 +14025,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -14207,7 +14071,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -14299,7 +14163,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -14391,7 +14255,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -14437,7 +14301,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -14483,7 +14347,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -14529,7 +14393,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -14575,7 +14439,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -14621,7 +14485,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -14667,7 +14531,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -14713,7 +14577,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -14759,7 +14623,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -14851,7 +14715,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -14897,7 +14761,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -14943,7 +14807,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -14989,7 +14853,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-17</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -15035,7 +14899,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -15081,7 +14945,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -15127,7 +14991,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -15173,7 +15037,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -15219,7 +15083,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -15265,7 +15129,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-03</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -15311,7 +15175,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -15357,7 +15221,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -15403,7 +15267,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -15449,7 +15313,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -15495,7 +15359,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -15541,7 +15405,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -15587,7 +15451,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -15633,7 +15497,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -15679,7 +15543,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -15725,7 +15589,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -15771,7 +15635,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-17</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -15817,7 +15681,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -15863,7 +15727,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -15909,7 +15773,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -15955,7 +15819,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -16001,7 +15865,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -16047,7 +15911,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -16093,7 +15957,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -16139,7 +16003,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -16185,7 +16049,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -16207,3085 +16071,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:M34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>映筑 - 映筑 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>337 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>47 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>284 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 457呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 454呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 452呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 456呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 409呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 393呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr"/>
-      <c r="I6" s="17" t="inlineStr"/>
-      <c r="J6" s="17" t="inlineStr"/>
-      <c r="K6" s="17" t="inlineStr"/>
-      <c r="L6" s="17" t="inlineStr"/>
-      <c r="M6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$995万
-$26,401/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$881万
-$26,053/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$767万
-$23,830/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$731万
-$22,696/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$842万
-$26,059/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$866万
-$26,888/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$854万
-$25,720/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$797万
-$24,682/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$758万
-$23,456/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K7" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$785万
-$23,796/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L7" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$811万
-$24,636/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M7" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$778万
-$24,163/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$990万
-$26,249/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$876万
-$25,905/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$742万
-$23,043/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$721万
-$22,404/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$837万
-$25,908/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$732万
-$22,725/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$875万
-$26,364/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$769万
-$23,795/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$785万
-$24,302/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K8" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$757万
-$22,941/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L8" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$784万
-$23,822/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M8" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$776万
-$24,095/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$984万
-$26,098/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$870万
-$25,754/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$763万
-$23,695/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$719万
-$22,339/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$807万
-$24,978/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$856万
-$26,587/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$870万
-$26,211/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$788万
-$24,394/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$780万
-$24,161/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K9" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$753万
-$22,813/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L9" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$782万
-$23,755/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M9" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$774万
-$24,024/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$978万
-$25,944/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$866万
-$25,607/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$738万
-$22,915/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$724万
-$22,497/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$827万
-$25,608/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$851万
-$26,438/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$865万
-$26,060/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$760万
-$23,518/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$752万
-$23,293/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K10" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$741万
-$22,446/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L10" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$804万
-$24,428/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M10" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$740万
-$22,986/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$972万
-$25,793/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$860万
-$25,456/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$759万
-$23,563/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$715万
-$22,207/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$806万
-$24,941/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$846万
-$26,286/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$860万
-$25,907/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$779万
-$24,109/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$748万
-$23,153/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K11" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$767万
-$23,256/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L11" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$769万
-$23,374/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M11" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$769万
-$23,880/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$967万
-$25,642/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$855万
-$25,308/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$737万
-$22,891/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$682万
-$21,183/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$817万
-$25,305/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$842万
-$26,137/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H12" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$727万
-$21,892/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$751万
-$23,239/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$767万
-$23,735/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$740万
-$22,420/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$794万
-$24,148/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M12" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$733万
-$22,779/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$845万
-$22,422/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$850万
-$25,157/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$746万
-$23,166/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$678万
-$21,059/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$788万
-$24,392/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$711万
-$22,087/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$842万
-$25,346/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$777万
-$24,065/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$762万
-$23,594/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K13" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$759万
-$22,986/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$756万
-$22,973/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M13" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$760万
-$23,597/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$890万
-$23,602/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$850万
-$25,157/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$716万
-$22,230/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$685万
-$21,281/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$812万
-$25,154/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$837万
-$25,984/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H14" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$808万
-$24,322/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$746万
-$23,102/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J14" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$739万
-$22,879/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K14" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$736万
-$22,289/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$796万
-$24,182/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M14" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$760万
-$23,597/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$878万
-$23,298/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$848万
-$25,083/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$744万
-$23,099/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$704万
-$21,878/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$777万
-$24,065/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$834万
-$25,910/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$848万
-$25,527/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I15" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$736万
-$22,791/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J15" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$729万
-$22,573/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K15" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$756万
-$22,920/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$785万
-$23,871/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M15" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$737万
-$22,882/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$840万
-$22,288/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$845万
-$25,009/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$739万
-$22,964/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$702万
-$21,814/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$783万
-$24,246/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$790万
-$24,543/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$803万
-$24,176/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$734万
-$22,724/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J16" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$735万
-$22,743/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K16" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$754万
-$22,854/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L16" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$749万
-$22,774/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M16" s="19" t="inlineStr">
-        <is>
-          <t>M | 323呎 (2房)
-$698万
-$21,606/呎
-(22年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$847万
-$22,457/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$843万
-$24,932/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$735万
-$22,831/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$700万
-$21,749/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$789万
-$24,424/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$830万
-$25,761/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H17" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$809万
-$24,358/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$763万
-$23,610/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J17" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$732万
-$22,674/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K17" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$722万
-$21,864/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L17" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$753万
-$22,879/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M17" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$703万
-$21,832/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$835万
-$22,155/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$840万
-$24,858/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$733万
-$22,767/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$698万
-$21,684/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$778万
-$24,098/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$827万
-$25,686/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$798万
-$24,033/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$730万
-$22,588/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="J18" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$753万
-$23,312/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K18" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$750万
-$22,719/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L18" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$774万
-$23,525/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M18" s="19" t="inlineStr">
-        <is>
-          <t>M | 323呎 (2房)
-$723万
-$22,377/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$833万
-$22,087/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$838万
-$24,784/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$709万
-$22,011/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$668万
-$20,743/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$800万
-$24,777/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$825万
-$25,609/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$837万
-$25,223/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$758万
-$23,466/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$728万
-$22,537/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K19" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$725万
-$21,966/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L19" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$741万
-$22,508/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M19" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$721万
-$22,380/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$830万
-$22,021/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$835万
-$24,710/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$729万
-$22,634/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$666万
-$20,679/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$798万
-$24,701/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$814万
-$25,279/呎
-(22年-04月)</t>
-        </is>
-      </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$793万
-$23,887/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$725万
-$22,450/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J20" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$748万
-$23,172/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K20" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$715万
-$21,668/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L20" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$769万
-$23,387/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M20" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$718万
-$22,312/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$863万
-$22,880/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$833万
-$24,633/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$697万
-$21,655/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$671万
-$20,834/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$795万
-$24,627/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$764万
-$23,738/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$791万
-$23,813/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$723万
-$22,379/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$716万
-$22,165/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$743万
-$22,515/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L21" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$767万
-$23,315/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M21" s="19" t="inlineStr">
-        <is>
-          <t>M | 323呎 (2房)
-$695万
-$21,503/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$825万
-$21,888/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$830万
-$24,559/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$703万
-$21,820/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$690万
-$21,417/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$777万
-$24,058/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$770万
-$23,919/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$805万
-$24,241/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$751万
-$23,251/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J22" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$744万
-$23,027/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K22" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$748万
-$22,676/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="L22" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$765万
-$23,245/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M22" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$714万
-$22,176/呎
-(22年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$860万
-$22,809/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$830万
-$24,559/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$725万
-$22,502/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$616万
-$19,125/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$793万
-$24,554/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$770万
-$23,919/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$797万
-$23,991/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I23" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$751万
-$23,251/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J23" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$744万
-$23,027/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="K23" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$718万
-$21,768/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L23" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$765万
-$23,245/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M23" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$714万
-$22,176/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$823万
-$21,822/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$828万
-$24,485/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$722万
-$22,435/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$688万
-$21,352/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$798万
-$24,721/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$792万
-$24,593/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$703万
-$21,178/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I24" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$749万
-$23,180/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="J24" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$742万
-$22,957/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K24" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$746万
-$22,609/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="L24" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$739万
-$22,474/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M24" s="19" t="inlineStr">
-        <is>
-          <t>M | 323呎 (2房)
-$676万
-$20,944/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$820万
-$21,754/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$825万
-$24,405/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$706万
-$21,918/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$672万
-$20,858/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$788万
-$24,400/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$790万
-$24,519/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$825万
-$24,837/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I25" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$746万
-$23,110/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J25" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$724万
-$22,424/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K25" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$714万
-$21,638/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L25" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$760万
-$23,107/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M25" s="19" t="inlineStr">
-        <is>
-          <t>M | 323呎 (2房)
-$703万
-$21,759/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$852万
-$22,599/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$822万
-$24,331/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$704万
-$21,852/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$663万
-$20,577/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$762万
-$23,590/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$787万
-$24,448/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$822万
-$24,762/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I26" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$744万
-$23,040/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J26" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$737万
-$22,816/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K26" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$734万
-$22,248/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L26" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$743万
-$22,572/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M26" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$672万
-$20,879/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$924万
-$24,504/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$817万
-$24,183/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$714万
-$22,170/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$659万
-$20,452/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$781万
-$24,174/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G27" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$782万
-$24,301/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$817万
-$24,611/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I27" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$739万
-$22,893/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$732万
-$22,675/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K27" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$730万
-$22,113/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L27" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$723万
-$21,971/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M27" s="19" t="inlineStr">
-        <is>
-          <t>M | 322呎 (2房)
-$696万
-$21,623/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$907万
-$24,048/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$777万
-$23,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$715万
-$22,193/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$673万
-$20,894/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$774万
-$23,963/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="G28" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$773万
-$24,006/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$812万
-$24,458/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$713万
-$22,062/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J28" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$728万
-$22,534/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$648万
-$19,625/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L28" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$731万
-$22,230/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M28" s="19" t="inlineStr">
-        <is>
-          <t>M | 323呎 (2房)
-$676万
-$20,922/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$854万
-$22,645/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$765万
-$22,642/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$708万
-$21,991/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$666万
-$20,698/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$742万
-$22,969/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$754万
-$23,425/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H29" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$762万
-$22,946/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$696万
-$21,556/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="J29" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$719万
-$22,249/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K29" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$716万
-$21,711/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L29" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$740万
-$22,484/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M29" s="19" t="inlineStr">
-        <is>
-          <t>M | 323呎 (2房)
-$683万
-$21,151/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$814万
-$21,596/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$784万
-$23,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$665万
-$20,637/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$658万
-$20,430/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$707万
-$21,894/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G30" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$644万
-$19,988/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H30" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$786万
-$23,685/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I30" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$719万
-$22,252/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J30" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$712万
-$22,037/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K30" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$703万
-$21,306/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="L30" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$731万
-$22,204/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M30" s="19" t="inlineStr">
-        <is>
-          <t>M | 323呎 (2房)
-$674万
-$20,882/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$811万
-$21,525/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$750万
-$22,196/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$688万
-$21,374/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$627万
-$19,481/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$712万
-$22,053/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G31" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$747万
-$23,203/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$752万
-$22,657/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$716万
-$22,181/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J31" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$710万
-$21,967/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K31" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$699万
-$21,171/呎
-(22年-01月)</t>
-        </is>
-      </c>
-      <c r="L31" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$726万
-$22,066/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M31" s="19" t="inlineStr">
-        <is>
-          <t>M | 323呎 (2房)
-$643万
-$19,906/呎
-(22年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>A | 377呎 (2房)
-$806万
-$21,382/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>B | 338呎 (2房)
-$777万
-$22,975/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>C | 322呎 (2房)
-$682万
-$21,165/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E32" s="19" t="inlineStr">
-        <is>
-          <t>D | 322呎 (2房)
-$647万
-$20,104/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (2房)
-$730万
-$22,592/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G32" s="19" t="inlineStr">
-        <is>
-          <t>F | 322呎 (2房)
-$742万
-$23,059/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H32" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (2房)
-$747万
-$22,511/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I32" s="19" t="inlineStr">
-        <is>
-          <t>H | 323呎 (2房)
-$698万
-$21,601/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J32" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (2房)
-$705万
-$21,826/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K32" s="19" t="inlineStr">
-        <is>
-          <t>K | 330呎 (2房)
-$694万
-$21,039/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L32" s="19" t="inlineStr">
-        <is>
-          <t>L | 329呎 (2房)
-$719万
-$21,855/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M32" s="19" t="inlineStr">
-        <is>
-          <t>M | 323呎 (2房)
-$637万
-$19,712/呎
-(22年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>A | 769呎 (3房)
-$835万
-$10,857/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>B | 323呎 (1房)
-$551万
-$17,044/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>C | 323呎 (1房)
-$553万
-$17,134/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E33" s="19" t="inlineStr">
-        <is>
-          <t>D | 447呎 (2房)
-$800万
-$17,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>E | 511呎 (2房)
-$861万
-$16,855/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G33" s="19" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$582万
-$18,029/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H33" s="19" t="inlineStr">
-        <is>
-          <t>G | 323呎 (1房)
-$582万
-$18,029/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I33" s="19" t="inlineStr">
-        <is>
-          <t>H | 331呎 (1房)
-$592万
-$17,896/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J33" s="19" t="inlineStr">
-        <is>
-          <t>J | 329呎 (1房)
-$569万
-$17,281/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K33" s="19" t="inlineStr">
-        <is>
-          <t>K | 323呎 (1房)
-$553万
-$17,134/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L33" s="17" t="inlineStr"/>
-      <c r="M33" s="17" t="inlineStr"/>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>A | 769呎 (3房)
-$1,127万
-$14,649/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>B | 326呎 (1房)
-$542万
-$16,626/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$770万
-$17,490/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E34" s="19" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$903万
-$17,675/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F34" s="19" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$568万
-$17,581/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G34" s="19" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$568万
-$17,581/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H34" s="19" t="inlineStr">
-        <is>
-          <t>G | 332呎 (1房)
-$578万
-$17,396/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I34" s="19" t="inlineStr">
-        <is>
-          <t>H | 329呎 (1房)
-$554万
-$16,833/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J34" s="19" t="inlineStr">
-        <is>
-          <t>J | 323呎 (1房)
-$539万
-$16,686/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K34" s="17" t="inlineStr"/>
-      <c r="L34" s="17" t="inlineStr"/>
-      <c r="M34" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-长沙湾-映筑.xlsx
+++ b/files/九龙-长沙湾-映筑.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="映筑" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -16071,4 +16250,3085 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>映筑 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 457呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 452呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 456呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 409呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 393呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+      <c r="K5" s="21" t="inlineStr"/>
+      <c r="L5" s="21" t="inlineStr"/>
+      <c r="M5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$995万
+$26,401/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$881万
+$26,053/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$767万
+$23,830/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$731万
+$22,696/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$842万
+$26,059/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$866万
+$26,888/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$854万
+$25,720/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$797万
+$24,682/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$758万
+$23,456/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$785万
+$23,796/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$811万
+$24,636/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$778万
+$24,163/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$990万
+$26,249/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$876万
+$25,905/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$742万
+$23,043/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$721万
+$22,404/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$837万
+$25,908/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$732万
+$22,725/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$875万
+$26,364/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$769万
+$23,795/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$785万
+$24,302/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$757万
+$22,941/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$784万
+$23,822/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="M7" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$776万
+$24,095/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$984万
+$26,098/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$870万
+$25,754/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$763万
+$23,695/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$719万
+$22,339/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$807万
+$24,978/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$856万
+$26,587/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$870万
+$26,211/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$788万
+$24,394/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$780万
+$24,161/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$753万
+$22,813/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$782万
+$23,755/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$774万
+$24,024/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$978万
+$25,944/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$866万
+$25,607/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$738万
+$22,915/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$724万
+$22,497/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$827万
+$25,608/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$851万
+$26,438/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$865万
+$26,060/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$760万
+$23,518/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$752万
+$23,293/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$741万
+$22,446/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$804万
+$24,428/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$740万
+$22,986/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$972万
+$25,793/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$860万
+$25,456/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$759万
+$23,563/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$715万
+$22,207/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$806万
+$24,941/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$846万
+$26,286/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$860万
+$25,907/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$779万
+$24,109/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$748万
+$23,153/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$767万
+$23,256/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$769万
+$23,374/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M10" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$769万
+$23,880/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$967万
+$25,642/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$855万
+$25,308/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$737万
+$22,891/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$682万
+$21,183/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$817万
+$25,305/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$842万
+$26,137/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$727万
+$21,892/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$751万
+$23,239/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$767万
+$23,735/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K11" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$740万
+$22,420/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$794万
+$24,148/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M11" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$733万
+$22,779/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$845万
+$22,422/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$850万
+$25,157/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$746万
+$23,166/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$678万
+$21,059/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$788万
+$24,392/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$711万
+$22,087/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$842万
+$25,346/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$777万
+$24,065/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$762万
+$23,594/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$759万
+$22,986/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$756万
+$22,973/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M12" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$760万
+$23,597/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$890万
+$23,602/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$850万
+$25,157/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$716万
+$22,230/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$685万
+$21,281/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$812万
+$25,154/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$837万
+$25,984/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$808万
+$24,322/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$746万
+$23,102/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$739万
+$22,879/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$736万
+$22,289/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$796万
+$24,182/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M13" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$760万
+$23,597/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$878万
+$23,298/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$848万
+$25,083/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$744万
+$23,099/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$704万
+$21,878/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$777万
+$24,065/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$834万
+$25,910/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$848万
+$25,527/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$736万
+$22,791/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$729万
+$22,573/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$756万
+$22,920/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$785万
+$23,871/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M14" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$737万
+$22,882/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$840万
+$22,288/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$845万
+$25,009/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$739万
+$22,964/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$702万
+$21,814/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$783万
+$24,246/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$790万
+$24,543/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$803万
+$24,176/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$734万
+$22,724/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$735万
+$22,743/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$754万
+$22,854/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$749万
+$22,774/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M15" s="23" t="inlineStr">
+        <is>
+          <t>M | 323呎 (2房)
+$698万
+$21,606/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$847万
+$22,457/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$843万
+$24,932/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$735万
+$22,831/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$700万
+$21,749/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$789万
+$24,424/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$830万
+$25,761/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$809万
+$24,358/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$763万
+$23,610/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$732万
+$22,674/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$722万
+$21,864/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$753万
+$22,879/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M16" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$703万
+$21,832/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$835万
+$22,155/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$840万
+$24,858/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$733万
+$22,767/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$698万
+$21,684/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$778万
+$24,098/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$827万
+$25,686/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$798万
+$24,033/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$730万
+$22,588/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$753万
+$23,312/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$750万
+$22,719/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L17" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$774万
+$23,525/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M17" s="23" t="inlineStr">
+        <is>
+          <t>M | 323呎 (2房)
+$723万
+$22,377/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$833万
+$22,087/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$838万
+$24,784/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$709万
+$22,011/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$668万
+$20,743/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$800万
+$24,777/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$825万
+$25,609/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$837万
+$25,223/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$758万
+$23,466/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$728万
+$22,537/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$725万
+$21,966/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$741万
+$22,508/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M18" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$721万
+$22,380/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$830万
+$22,021/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$835万
+$24,710/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$729万
+$22,634/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$666万
+$20,679/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$798万
+$24,701/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$814万
+$25,279/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$793万
+$23,887/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$725万
+$22,450/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$748万
+$23,172/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K19" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$715万
+$21,668/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$769万
+$23,387/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M19" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$718万
+$22,312/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$863万
+$22,880/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$833万
+$24,633/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$697万
+$21,655/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$671万
+$20,834/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$795万
+$24,627/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$764万
+$23,738/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$791万
+$23,813/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$723万
+$22,379/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$716万
+$22,165/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$743万
+$22,515/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L20" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$767万
+$23,315/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M20" s="23" t="inlineStr">
+        <is>
+          <t>M | 323呎 (2房)
+$695万
+$21,503/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$825万
+$21,888/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$830万
+$24,559/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$703万
+$21,820/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$690万
+$21,417/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$777万
+$24,058/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$770万
+$23,919/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$805万
+$24,241/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$751万
+$23,251/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$744万
+$23,027/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$748万
+$22,676/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$765万
+$23,245/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M21" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$714万
+$22,176/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$860万
+$22,809/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$830万
+$24,559/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$725万
+$22,502/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$616万
+$19,125/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$793万
+$24,554/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$770万
+$23,919/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$797万
+$23,991/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$751万
+$23,251/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$744万
+$23,027/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$718万
+$21,768/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$765万
+$23,245/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M22" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$714万
+$22,176/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$823万
+$21,822/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$828万
+$24,485/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$722万
+$22,435/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$688万
+$21,352/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$798万
+$24,721/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$792万
+$24,593/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$703万
+$21,178/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$749万
+$23,180/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$742万
+$22,957/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$746万
+$22,609/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="L23" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$739万
+$22,474/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M23" s="23" t="inlineStr">
+        <is>
+          <t>M | 323呎 (2房)
+$676万
+$20,944/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$820万
+$21,754/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$825万
+$24,405/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$706万
+$21,918/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$672万
+$20,858/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$788万
+$24,400/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$790万
+$24,519/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$825万
+$24,837/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$746万
+$23,110/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$724万
+$22,424/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$714万
+$21,638/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$760万
+$23,107/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M24" s="23" t="inlineStr">
+        <is>
+          <t>M | 323呎 (2房)
+$703万
+$21,759/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$852万
+$22,599/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$822万
+$24,331/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$704万
+$21,852/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$663万
+$20,577/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$762万
+$23,590/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$787万
+$24,448/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$822万
+$24,762/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$744万
+$23,040/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$737万
+$22,816/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$734万
+$22,248/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L25" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$743万
+$22,572/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M25" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$672万
+$20,879/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$924万
+$24,504/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$817万
+$24,183/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$714万
+$22,170/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$659万
+$20,452/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$781万
+$24,174/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$782万
+$24,301/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$817万
+$24,611/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$739万
+$22,893/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$732万
+$22,675/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$730万
+$22,113/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L26" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$723万
+$21,971/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M26" s="23" t="inlineStr">
+        <is>
+          <t>M | 322呎 (2房)
+$696万
+$21,623/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$907万
+$24,048/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$777万
+$23,000/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$715万
+$22,193/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$673万
+$20,894/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$774万
+$23,963/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$773万
+$24,006/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$812万
+$24,458/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$713万
+$22,062/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$728万
+$22,534/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$648万
+$19,625/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L27" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$731万
+$22,230/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M27" s="23" t="inlineStr">
+        <is>
+          <t>M | 323呎 (2房)
+$676万
+$20,922/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$854万
+$22,645/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$765万
+$22,642/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$708万
+$21,991/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$666万
+$20,698/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$742万
+$22,969/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$754万
+$23,425/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$762万
+$22,946/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$696万
+$21,556/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$719万
+$22,249/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$716万
+$21,711/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L28" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$740万
+$22,484/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M28" s="23" t="inlineStr">
+        <is>
+          <t>M | 323呎 (2房)
+$683万
+$21,151/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$814万
+$21,596/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$784万
+$23,200/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$665万
+$20,637/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$658万
+$20,430/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$707万
+$21,894/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$644万
+$19,988/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$786万
+$23,685/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$719万
+$22,252/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$712万
+$22,037/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$703万
+$21,306/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="L29" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$731万
+$22,204/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M29" s="23" t="inlineStr">
+        <is>
+          <t>M | 323呎 (2房)
+$674万
+$20,882/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$811万
+$21,525/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$750万
+$22,196/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$688万
+$21,374/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$627万
+$19,481/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$712万
+$22,053/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$747万
+$23,203/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$752万
+$22,657/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$716万
+$22,181/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$710万
+$21,967/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$699万
+$21,171/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="L30" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$726万
+$22,066/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M30" s="23" t="inlineStr">
+        <is>
+          <t>M | 323呎 (2房)
+$643万
+$19,906/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 377呎 (2房)
+$806万
+$21,382/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 338呎 (2房)
+$777万
+$22,975/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>C | 322呎 (2房)
+$682万
+$21,165/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>D | 322呎 (2房)
+$647万
+$20,104/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (2房)
+$730万
+$22,592/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>F | 322呎 (2房)
+$742万
+$23,059/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (2房)
+$747万
+$22,511/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>H | 323呎 (2房)
+$698万
+$21,601/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (2房)
+$705万
+$21,826/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>K | 330呎 (2房)
+$694万
+$21,039/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="L31" s="23" t="inlineStr">
+        <is>
+          <t>L | 329呎 (2房)
+$719万
+$21,855/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="M31" s="23" t="inlineStr">
+        <is>
+          <t>M | 323呎 (2房)
+$637万
+$19,712/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>A | 769呎 (3房)
+$835万
+$10,857/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>B | 323呎 (1房)
+$551万
+$17,044/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>C | 323呎 (1房)
+$553万
+$17,134/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+$800万
+$17,900/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>E | 511呎 (2房)
+$861万
+$16,855/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$582万
+$18,029/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>G | 323呎 (1房)
+$582万
+$18,029/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>H | 331呎 (1房)
+$592万
+$17,896/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>J | 329呎 (1房)
+$569万
+$17,281/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>K | 323呎 (1房)
+$553万
+$17,134/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr"/>
+      <c r="M32" s="21" t="inlineStr"/>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>A | 769呎 (3房)
+$1127万
+$14,649/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>B | 326呎 (1房)
+$542万
+$16,626/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$770万
+$17,490/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$903万
+$17,675/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$568万
+$17,581/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$568万
+$17,581/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>G | 332呎 (1房)
+$578万
+$17,396/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>H | 329呎 (1房)
+$554万
+$16,833/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>J | 323呎 (1房)
+$539万
+$16,686/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="K33" s="21" t="inlineStr"/>
+      <c r="L33" s="21" t="inlineStr"/>
+      <c r="M33" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-长沙湾-映筑.xlsx
+++ b/files/九龙-长沙湾-映筑.xlsx
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
